--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FE-2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LUU_BT\CV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE6A3AE8-30F0-4497-8353-CA67333802AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CD75CD-A459-4C76-BA0A-D608927F3546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{87B98776-3E28-4B6B-95D7-73F7C11CAC83}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
   <si>
     <t>Lập trình Font-end web 2</t>
   </si>
@@ -58,6 +58,122 @@
   </si>
   <si>
     <t>Thành viên thức hiện</t>
+  </si>
+  <si>
+    <t>Triều</t>
+  </si>
+  <si>
+    <t>Tạo bánh xe Wheel: 
+- Tạo hình hộp chữ nhật bằng BoxGeometry
+- Sử dụng thuộc tính MeshLambertMaterial thiết kế chất liệu bánh xe màu đen
+- flatShading làm cho mặt phẳng sắc nét hơn
+- Tạo mô hình 3D từ thuộc tính Mesh
+- Wheel.position.z = 6 * zoom; đặt bánh xe nhô ra phía trước theo trục Z</t>
+  </si>
+  <si>
+    <t>Tạo scene 3D hiển thị màn hình:
+- Tạo đối tượng kiểu WebGLRenderer với tham số alpha true làm cho nền trong suốt
+- antialias: true làm mịn cạnh
+- Bật đổ bóng renderer.shadowMap.enabled = true;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tạo ánh sáng tự nhiên hemiLight :
+- Tạo đối tượng kiểu HemisphereLight với 3 thuộc tính màu trời, màu đất, cường độ sáng.
+- DirectionalLight ánh sáng mặt trời đặt góc chiếu ở tọa độ ở bên trái và ở trên trong 3D.
+- Tạo hướng sáng với màu và cường độ sáng. Đặt vị trí cho nguồn sáng tọa độ trong không gian (x, y, z) (-100, -100, 200) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tạo làn đường xe chạy generateLanes: 
+- Tạo ra làn đường đặt theo trục Y để trải đề các làn,
+- Thêm vào mesh để hiển thị và trả về lane </t>
+  </si>
+  <si>
+    <t>Thiết lập góc nhìn:
+- Tạo đối tượng scene thiết lập môi trường 3D chứa mesh, ánh sáng và camera.
+- Đặt khoảng cách distance từ camera đến giao diện là 500. 
+- Xoay camera theo 3 trục x, y, z để có được góc nhìn từ trên xuống</t>
+  </si>
+  <si>
+    <t>Chức năng thêm thảm cỏ:
+- Khi người dùng đi hết các lane xe thì sẽ tạo ra các lane cỏ vạch đích, đặt ở cuối bản đồ và thêm vào mảng lane
+- Thêm lưới 3D cho cỏ, đặt cỏ theo trục Y của bản đồ</t>
+  </si>
+  <si>
+    <t>Chức năng di chuyển:
+- Tạo 4 nút di chuyển đi thẳng, rẽ trái, rẽ phải, đi lui, bắt sự kiện click và sự kiện keydown của bàn phím khi nhấn lên, xuống, trái, phải nhân vật đi theo hướng điều khiển</t>
+  </si>
+  <si>
+    <t>Chức năng thêm lane: 
+- Tạo 1 đối tượng kiểu Lane sau đó gắn vị trí cho lane, thêm vào cảnh scene để hiển thị trên màn hình và lưu vào mảng lanes.</t>
+  </si>
+  <si>
+    <t>Tạo xe con:
+- Tạo 1 đối tượng group chứa tất cả các xe
+- Tạo màu ngẫu nhiên cho các xe
+- Tạo thân xe kiểu BoxGeometry với dài: 60, rộng: 30, cao: 15 nhân zoom để điều chỉnh tỉ lệ
+- Đổ bóng cho thân xe: sử dụng MeshPhongMaterial với màu sắc và độ sắc nét cho bóng
+- Tạo cabin nóc kiểu BoxGeometry ghép 4 mặt vật liệu đã tạo trước đó carBackTexture, carFrontTexture, carRightSideTexture, carLeftSideTexture.
+- Gắn bánh xe vào sử dụng hàm Wheel()
+- Trả về hoàn chỉnh đối tượng kiểu Car() và hiển thị</t>
+  </si>
+  <si>
+    <t>Tạo xe tải: 
+- Tạo 1 đối tượng group chứa tất cả các xe
+- Tạo màu ngẫu nhiên cho các xe
+- Tạo đáy cho xe (d: 100, r: 25, h: 5) thêm đổ bóng sử dụng MeshLambertMaterial
+- Tạo thùng hàng ()
+- Thiết lập vị trí cargo.position.x = 15 * zoom;cargo.position.z = 30 * zoom; theo trục x lùi về giữa và trục z cao hơn đấy
+- Tạo cabin xe tải ghép các mặt truckFrontTexture, truckRightSideTexture, truckLeftSideTexture
+- Thêm bánh xe sử dụng hàm Wheel() sau đó trả về đối tượng truck.</t>
+  </si>
+  <si>
+    <t>Tạo cây:
+- Tạo 1 nhóm để gom các cây
+- Tạo thân cây sử dụng thuộc tính hình hộp BoxGeometry thiết lập kích thước cho cây (15, 15, 20)
+- Đổ bóng cho cây có thêm màu và độ sắc nét
+- trunk.position.z = 10 * zoom; đặt phần thân nhô lên 1 nữa chiều cao vì tâm mặc định ở giữa box
+- trunk.castShadow = true; trunk.receiveShadow = true; cho phép thân cây đổ bóng
+- Thêm cây vào nhóm cây
+- Tán cây height lấy ngẫu nhiên chiều cao cho lá
+- Gộp tán lá với thân cây sử dụng thuộc tính Mesh
+- crown.position.z = (height / 2 + 20) * zoom; tính vị trí lá 20 * zoom là chiều cao thân cây, (height / 2) * zoom là nửa chiều cao của tán lá vừa nằm ngay trên đầu thân cây</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tạo con gà:
+- Tạo 1 group để gộp lại các thành phần của con gà
+- Tạo thân con gà dạng hình hộp chữ nhật BoxGeometry gắn kích thước, màu sắc,flatShading: true:  bóng nhẹ
+-body.position.z = 10 * zoom;  thân gà nằm đúng lên mặt phẳng 
+- body.castShadow = true; body.receiveShadow = true; đổ bóng cho gà 
+- Tạo mào gà thiết lập mào gà bằng BoxGeometry, thêm màu đỏ 
+- rowel.position.z = 21 * zoom; đặt mào gà ở trên thân gà cao hơn 1 so với thân gà
+- Trà về mô hình gà </t>
+  </si>
+  <si>
+    <t>Tạo mặt đường
+- Tạo 1 group gộp tất cả các thành phần của mặt đường lại
+- Tạo mặt phẳng con đường thiết lập chiều dài và rộng, màu sắc dựa vào thuộc tính PlaneGeometry là tạo mặt phẳng nằm ngang
+- MeshPhongMaterial phản xạ ánh sáng để dễ thấy đường
+- const middle = createSection(0x454A59); phần giữa mặt đường màu xám cho giống đường nhựa
+- const left = createSection(0x393D49); phần trái mặt đường 
+- const right = createSection(0x393D49); mặt phải của đường 
+- Sau đó trả về biến road</t>
+  </si>
+  <si>
+    <t>Tạo bãi cỏ
+- Tạo 1 group gộp tất cẩ các thành phần của cỏ
+- Tạo bãi cỏ bằng thuộc tính BoxGeometry thiết lập kích thước, thêm màu sắc, đổ bóng</t>
+  </si>
+  <si>
+    <t>Hiệu ứng Chiến thắng:
+- Khi người chơi nhảy đến lane cuối hiển thị chữ Victory từ mờ đến rõ, 1 màu vàng tỏa ra từ tâm của chữ và có thêm đóm vàng bay ra từ 2 bên chữ Victory kèm theo nhạc</t>
+  </si>
+  <si>
+    <t>Hiệu ứng khi gà bị xe đụng:
+- Kiểm tra thấy gà bị xe đụng ngây lập tức bay lên trời theo hướng xe</t>
+  </si>
+  <si>
+    <t>Hiệu ứng xe di chuyển:
+- Di chuyển đều từ trái sang phải hoặc phải sang trái</t>
   </si>
 </sst>
 </file>
@@ -90,9 +206,53 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
@@ -102,13 +262,58 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -424,30 +629,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2283FBF-3593-4636-9371-AAACD1430F10}">
-  <dimension ref="B2:I41"/>
+  <dimension ref="B2:I51"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="7" width="20.59765625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
     </row>
     <row r="3" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4">
@@ -466,163 +674,517 @@
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1" t="s">
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="I10" s="8"/>
+    </row>
+    <row r="11" spans="2:9" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C11" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="17"/>
+    </row>
+    <row r="12" spans="2:9" ht="52.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C12" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="17"/>
+    </row>
+    <row r="13" spans="2:9" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>3</v>
       </c>
+      <c r="C13" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" s="17"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>4</v>
       </c>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>5</v>
       </c>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>6</v>
       </c>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>7</v>
       </c>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>8</v>
       </c>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>9</v>
       </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>10</v>
       </c>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>5</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1" t="s">
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="I30" s="1"/>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32">
+      <c r="I30" s="8"/>
+    </row>
+    <row r="31" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="2:9" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33">
+      <c r="C32" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32" s="6"/>
+    </row>
+    <row r="33" spans="2:9" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B34">
+      <c r="C33" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I33" s="7"/>
+    </row>
+    <row r="34" spans="2:9" ht="70.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B35">
+      <c r="C34" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I34" s="4"/>
+    </row>
+    <row r="35" spans="2:9" ht="101.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B36">
+      <c r="C35" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" s="3"/>
+    </row>
+    <row r="36" spans="2:9" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B37">
+      <c r="C36" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I36" s="4"/>
+    </row>
+    <row r="37" spans="2:9" ht="117.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B38">
+      <c r="C37" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I37" s="4"/>
+    </row>
+    <row r="38" spans="2:9" ht="89.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B39">
+      <c r="C38" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I38" s="4"/>
+    </row>
+    <row r="39" spans="2:9" ht="118.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B40">
+      <c r="C39" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I39" s="4"/>
+    </row>
+    <row r="40" spans="2:9" ht="208.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B41">
+      <c r="C40" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I40" s="4"/>
+    </row>
+    <row r="41" spans="2:9" ht="180.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="2">
         <v>10</v>
       </c>
+      <c r="C41" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I41" s="4"/>
+    </row>
+    <row r="42" spans="2:9" ht="231" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="2">
+        <v>11</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I42" s="4"/>
+    </row>
+    <row r="43" spans="2:9" ht="161.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="2">
+        <v>12</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I43" s="4"/>
+    </row>
+    <row r="44" spans="2:9" ht="153" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="2">
+        <v>13</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I44" s="4"/>
+    </row>
+    <row r="45" spans="2:9" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="2">
+        <v>14</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I45" s="4"/>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B46" s="2">
+        <v>15</v>
+      </c>
+      <c r="C46" s="11"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B47" s="2">
+        <v>16</v>
+      </c>
+      <c r="C47" s="11"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B48" s="2">
+        <v>17</v>
+      </c>
+      <c r="C48" s="11"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B49" s="2">
+        <v>18</v>
+      </c>
+      <c r="C49" s="11"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B50" s="2">
+        <v>19</v>
+      </c>
+      <c r="C50" s="11"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B51" s="2">
+        <v>20</v>
+      </c>
+      <c r="C51" s="11"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="61">
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
     <mergeCell ref="C30:G30"/>
     <mergeCell ref="H30:I30"/>
     <mergeCell ref="B2:H2"/>
@@ -631,7 +1193,36 @@
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="B29:I29"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="H41:I41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>